--- a/Result/profitability/5906.xlsx
+++ b/Result/profitability/5906.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.19125</v>
+        <v>0.13</v>
       </c>
       <c r="N2" t="n">
-        <v>54.46375</v>
+        <v>54.44125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5812499999999999</v>
+        <v>0.52125</v>
       </c>
       <c r="N3" t="n">
-        <v>53.4075</v>
+        <v>52.98375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>15.7</v>
       </c>
       <c r="M4" t="n">
-        <v>2.49625</v>
+        <v>2.4375</v>
       </c>
       <c r="N4" t="n">
-        <v>53.1925</v>
+        <v>53.00625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>2.49625</v>
+        <v>2.41</v>
       </c>
       <c r="N5" t="n">
-        <v>51.97875</v>
+        <v>51.43375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>2.37</v>
+        <v>2.3775</v>
       </c>
       <c r="N6" t="n">
-        <v>51.4075</v>
+        <v>51.0225</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>2.49625</v>
+        <v>2.45875</v>
       </c>
       <c r="N7" t="n">
-        <v>50.31625</v>
+        <v>50.395</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>2.675</v>
+        <v>2.64875</v>
       </c>
       <c r="N8" t="n">
-        <v>50.59</v>
+        <v>50.25625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5906</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>397</v>
+      </c>
+      <c r="D70" t="n">
+        <v>186</v>
+      </c>
+      <c r="E70" t="n">
+        <v>211</v>
+      </c>
+      <c r="F70" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-1.28%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="N70" t="n">
+        <v>55.0375</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-1.909090909090909</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-2.670000000000002</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.04777241009125066</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-1.169491525423729</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-4.359999999999999</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.07572073636679399</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
